--- a/재원/20250110_DataDictionary_재원.xlsx
+++ b/재원/20250110_DataDictionary_재원.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Project\Team3\재원\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08774CDE-15B8-4300-AB55-485F2866B724}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58F9885F-46B9-4456-A74E-69FC956451F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{8F881B30-87A6-47BA-921E-F312CF413D6B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8F881B30-87A6-47BA-921E-F312CF413D6B}"/>
   </bookViews>
   <sheets>
     <sheet name="샘플 데이터목록" sheetId="1" r:id="rId1"/>
